--- a/output/pdf_financials_xlsx/MUSL.xlsx
+++ b/output/pdf_financials_xlsx/MUSL.xlsx
@@ -8677,7 +8677,7 @@
         <v>-5.807362</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>0.128769</v>
+        <v>-0.128769</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MUSL.xlsx
+++ b/output/pdf_financials_xlsx/MUSL.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000539</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.146845</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.024495</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000539</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.146845</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.024495</v>
       </c>
     </row>
     <row r="37">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.063939</v>
+        <v>0.0634</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.564323</v>
+        <v>0.417478</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/MUSL.xlsx
+++ b/output/pdf_financials_xlsx/MUSL.xlsx
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.029073</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5144,7 +5144,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>0.024058</v>
       </c>
@@ -5175,7 +5179,11 @@
           <t>Depreciation of right-of-use asset 8</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>0.005015</v>
       </c>
@@ -5359,7 +5367,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>0.000621</v>
       </c>
@@ -5826,7 +5838,11 @@
           <t>Proceeds from sales of property and equipment</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>0.0005</v>
       </c>

--- a/output/pdf_financials_xlsx/MUSL.xlsx
+++ b/output/pdf_financials_xlsx/MUSL.xlsx
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.143781</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.188575</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.473968</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.279722</v>
       </c>
     </row>
     <row r="116">
@@ -4532,7 +4532,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -4993,7 +4997,11 @@
           <t>Accretion expense 12</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.143781</v>
       </c>
@@ -5807,7 +5815,11 @@
           <t>Proceed from sale of investments 7</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
